--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Zählstatus einer Behandlungslinie nach EnLiST (Saini et al., Ann Oncol 2026): in der LoT-Zählung, außerhalb der Zählung oder investigationale Studientherapie (iLoT).</t>
+    <t>Zählstatus einer Behandlungslinie nach EnLiST: auf einer LoT-Zählachse (counted) oder außerhalb jeder Zählung (not-counted, z. B. lokoregionale Behandlungslinie).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,7 +144,7 @@
     <t>Zählt in der LoT-Zählung</t>
   </si>
   <si>
-    <t>Systemische Therapielinie, die nach EnLiST in die Linien-Zählung eingeht.</t>
+    <t>Systemische Therapielinie auf einer EnLiST-Zählachse (eLoT, aLoT oder iLoT); die Designation steht in der Extension enlist-lot.</t>
   </si>
   <si>
     <t>not-counted</t>
@@ -153,16 +153,7 @@
     <t>Zählt nicht</t>
   </si>
   <si>
-    <t>Behandlungslinie außerhalb der EnLiST-Zählung — z. B. lokoregionale Behandlungslinie (Chirurgie, Strahlentherapie, Ablation).</t>
-  </si>
-  <si>
-    <t>investigational</t>
-  </si>
-  <si>
-    <t>iLoT — Studientherapie</t>
-  </si>
-  <si>
-    <t>Investigational Line of Therapy nach EnLiST: Studientherapie, separat notiert statt regulär gezählt.</t>
+    <t>Behandlungslinie außerhalb jeder EnLiST-Zählachse — z. B. lokoregionale Behandlungslinie (Chirurgie, Strahlentherapie, Ablation) oder Management-Abschnitt.</t>
   </si>
 </sst>
 </file>
@@ -470,7 +461,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -515,20 +506,6 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-enlist-countable.xlsx
+++ b/ci-build/CodeSystem-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
